--- a/data/trans_orig/P1415-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1415-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de problemas crónicos de la piel en 2012</t>
+          <t>Población con diagnóstico de problemas crónicos de la piel en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9957</t>
+          <t>9435</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27274</t>
+          <t>26091</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18355</t>
+          <t>18639</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17181</t>
+          <t>17326</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38931</t>
+          <t>38943</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>676195</t>
+          <t>677378</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>693512</t>
+          <t>694034</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>678695</t>
+          <t>678411</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>691927</t>
+          <t>691705</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1361588</t>
+          <t>1361576</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1383338</t>
+          <t>1383193</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9331</t>
+          <t>9641</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27771</t>
+          <t>27126</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14184</t>
+          <t>15070</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15463</t>
+          <t>15739</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36076</t>
+          <t>37102</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>990176</t>
+          <t>990821</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1008616</t>
+          <t>1008306</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1014789</t>
+          <t>1013903</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1025767</t>
+          <t>1025808</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2010845</t>
+          <t>2009819</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2031458</t>
+          <t>2031182</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>19452</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17017</t>
+          <t>18351</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11472</t>
+          <t>12092</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30954</t>
+          <t>31767</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>736454</t>
+          <t>738171</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>753265</t>
+          <t>753236</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>760157</t>
+          <t>758823</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>772274</t>
+          <t>772155</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1503843</t>
+          <t>1503030</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1523325</t>
+          <t>1522705</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6951</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23873</t>
+          <t>24424</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>18802</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>14323</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38912</t>
+          <t>36215</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>923866</t>
+          <t>923315</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>940788</t>
+          <t>940590</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1033993</t>
+          <t>1033099</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1048387</t>
+          <t>1047911</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1960728</t>
+          <t>1963425</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1983988</t>
+          <t>1985317</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42583</t>
+          <t>42737</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75958</t>
+          <t>76481</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26002</t>
+          <t>25331</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52895</t>
+          <t>50590</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77082</t>
+          <t>72883</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116625</t>
+          <t>114447</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3350821</t>
+          <t>3350298</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3384196</t>
+          <t>3384042</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3502203</t>
+          <t>3504508</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3529096</t>
+          <t>3529767</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6865252</t>
+          <t>6867430</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6904795</t>
+          <t>6908994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de problemas crónicos de la piel en 2016</t>
+          <t>Población con diagnóstico de problemas crónicos de la piel en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>15470</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16648</t>
+          <t>16960</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>668045</t>
+          <t>668336</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>657688</t>
+          <t>657369</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>669560</t>
+          <t>669757</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1330991</t>
+          <t>1330679</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1343257</t>
+          <t>1343160</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16577</t>
+          <t>16629</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13019</t>
+          <t>12587</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30049</t>
+          <t>30305</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20406</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42022</t>
+          <t>41908</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1005854</t>
+          <t>1005802</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1018460</t>
+          <t>1018295</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1012864</t>
+          <t>1012608</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1029894</t>
+          <t>1030326</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2023322</t>
+          <t>2023436</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2044938</t>
+          <t>2045261</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9618</t>
+          <t>9473</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>10893</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30277</t>
+          <t>29429</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14616</t>
+          <t>14567</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36734</t>
+          <t>36085</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>749934</t>
+          <t>750079</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>757881</t>
+          <t>757867</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>754734</t>
+          <t>755582</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>774214</t>
+          <t>774118</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1507829</t>
+          <t>1508478</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1529947</t>
+          <t>1529996</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11680</t>
+          <t>12526</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29296</t>
+          <t>30042</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17905</t>
+          <t>17990</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20114</t>
+          <t>20965</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43271</t>
+          <t>43981</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>908271</t>
+          <t>907525</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>925887</t>
+          <t>925041</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1025874</t>
+          <t>1025789</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1038813</t>
+          <t>1038687</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1938075</t>
+          <t>1937365</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1961232</t>
+          <t>1960381</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25154</t>
+          <t>25074</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48157</t>
+          <t>48341</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42821</t>
+          <t>41393</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72320</t>
+          <t>74023</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74075</t>
+          <t>74417</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114000</t>
+          <t>112707</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3346193</t>
+          <t>3346009</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3369196</t>
+          <t>3369276</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3472222</t>
+          <t>3470519</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3501721</t>
+          <t>3503149</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6824892</t>
+          <t>6826185</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6864817</t>
+          <t>6864475</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/P1415-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1415-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9435</t>
+          <t>9097</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26091</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18639</t>
+          <t>17924</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17326</t>
+          <t>17716</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38943</t>
+          <t>37660</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>677378</t>
+          <t>676403</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>694034</t>
+          <t>694372</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>678411</t>
+          <t>679126</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>691705</t>
+          <t>691562</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1361576</t>
+          <t>1362859</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1383193</t>
+          <t>1382803</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t>10019</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27126</t>
+          <t>27764</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>15721</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15739</t>
+          <t>15494</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37102</t>
+          <t>36850</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>990821</t>
+          <t>990183</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1008306</t>
+          <t>1007928</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1013903</t>
+          <t>1013252</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1025808</t>
+          <t>1025826</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2009819</t>
+          <t>2010071</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2031182</t>
+          <t>2031427</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19452</t>
+          <t>19797</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18351</t>
+          <t>17820</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>11870</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31767</t>
+          <t>31595</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>738171</t>
+          <t>737826</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>753236</t>
+          <t>753292</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>758823</t>
+          <t>759354</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>772155</t>
+          <t>772179</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1503030</t>
+          <t>1503202</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1522705</t>
+          <t>1522927</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24424</t>
+          <t>24028</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18802</t>
+          <t>19582</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14323</t>
+          <t>14677</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36215</t>
+          <t>37209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>923315</t>
+          <t>923711</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>940590</t>
+          <t>940026</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1033099</t>
+          <t>1032319</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1047911</t>
+          <t>1047946</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1963425</t>
+          <t>1962431</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1985317</t>
+          <t>1984963</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42737</t>
+          <t>42357</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76481</t>
+          <t>75389</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25331</t>
+          <t>27192</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50590</t>
+          <t>53439</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72883</t>
+          <t>75669</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114447</t>
+          <t>116553</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3350298</t>
+          <t>3351390</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3384042</t>
+          <t>3384422</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3504508</t>
+          <t>3501659</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3529767</t>
+          <t>3527906</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6867430</t>
+          <t>6865324</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6908994</t>
+          <t>6906208</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>6750</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15470</t>
+          <t>14017</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16960</t>
+          <t>17160</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>668336</t>
+          <t>668050</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>657369</t>
+          <t>658822</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>669757</t>
+          <t>669667</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1330679</t>
+          <t>1330479</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1343160</t>
+          <t>1343223</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16629</t>
+          <t>17524</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12587</t>
+          <t>12849</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30305</t>
+          <t>30482</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20388</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41908</t>
+          <t>40651</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1005802</t>
+          <t>1004907</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1018295</t>
+          <t>1018299</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1012608</t>
+          <t>1012431</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1030326</t>
+          <t>1030064</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2023436</t>
+          <t>2024693</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2045261</t>
+          <t>2044956</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>9757</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10893</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29429</t>
+          <t>29317</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14567</t>
+          <t>14344</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36085</t>
+          <t>35570</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>750079</t>
+          <t>749795</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>757867</t>
+          <t>757827</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>755582</t>
+          <t>755694</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>774118</t>
+          <t>773425</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1508478</t>
+          <t>1508993</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1529996</t>
+          <t>1530219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12526</t>
+          <t>12772</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30042</t>
+          <t>31477</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17990</t>
+          <t>17868</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20965</t>
+          <t>20508</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43981</t>
+          <t>42982</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>907525</t>
+          <t>906090</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>925041</t>
+          <t>924795</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1025789</t>
+          <t>1025911</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1038687</t>
+          <t>1038792</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1937365</t>
+          <t>1938364</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1960381</t>
+          <t>1960838</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25074</t>
+          <t>24162</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48341</t>
+          <t>49154</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41393</t>
+          <t>43365</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74023</t>
+          <t>72730</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74417</t>
+          <t>74796</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112707</t>
+          <t>112608</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3346009</t>
+          <t>3345196</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3369276</t>
+          <t>3370188</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3470519</t>
+          <t>3471812</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3503149</t>
+          <t>3501177</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6826185</t>
+          <t>6826284</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6864475</t>
+          <t>6864096</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
